--- a/test-results/excel-reports/prod_report_2026-05-07.xlsx
+++ b/test-results/excel-reports/prod_report_2026-05-07.xlsx
@@ -63,7 +63,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>52.19</t>
+    <t>48.99</t>
   </si>
   <si>
     <t>tests\ui\regressionTest.prod.spec.ts</t>
@@ -72,7 +72,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-05-07T08:26:56.156Z</t>
+    <t>2026-05-07T08:58:33.240Z</t>
   </si>
   <si>
     <t>PROD</t>
@@ -90,7 +90,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>5/7/2026, 2:26:57 PM</t>
+    <t>5/7/2026, 2:58:33 PM</t>
   </si>
   <si>
     <t>Total Tests</t>
@@ -126,7 +126,7 @@
     <t>Avg Duration (ms)</t>
   </si>
   <si>
-    <t>52185.00</t>
+    <t>48995.00</t>
   </si>
   <si>
     <t>passed</t>
@@ -629,7 +629,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2">
-        <v>52185</v>
+        <v>48995</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>16</v>
